--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4004004932a74030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf5f8591ef234e19"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf5f8591ef234e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8b6894ec4c046e4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8b6894ec4c046e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra255d4df2392488a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra255d4df2392488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R959dba6a5a2445cb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R959dba6a5a2445cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb6dfbaca62b4153"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb6dfbaca62b4153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b787b761f394ab7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b787b761f394ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6041df746e0e4b39"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6041df746e0e4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7949e8deb884467c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7949e8deb884467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30809133f1c74bab"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30809133f1c74bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb88ee371dea04192"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb88ee371dea04192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7b4aab19cc640af"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7b4aab19cc640af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra53cc3d61854444f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra53cc3d61854444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rabe79651dbf24bca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rabe79651dbf24bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9f1265bb8df43b6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9f1265bb8df43b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fd5b49adbfc4fb5"/>
   </x:sheets>
 </x:workbook>
 </file>
